--- a/public/FileSettingTemplet/ProductionItem.xlsx
+++ b/public/FileSettingTemplet/ProductionItem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NhatTruong\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F8B9A2-1E5F-485F-9406-ED7CE72C0CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C13B1A4-ABCE-47EB-8782-8BF367905A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3017" yWindow="3017" windowWidth="18514" windowHeight="10740" xr2:uid="{5FD91716-440A-47B0-8883-6349B069A461}"/>
+    <workbookView xWindow="4106" yWindow="3094" windowWidth="18514" windowHeight="10740" xr2:uid="{5FD91716-440A-47B0-8883-6349B069A461}"/>
   </bookViews>
   <sheets>
     <sheet name="Trang_tính1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="13">
   <si>
     <t>tên món</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>Đồ uống</t>
+  </si>
+  <si>
+    <t>Thời gian</t>
   </si>
 </sst>
 </file>
@@ -174,15 +177,15 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -517,14 +520,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{244520F9-2B64-4781-A622-EEA6E3DDF8AC}">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="15" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15" style="2" customWidth="1"/>
     <col min="8" max="8" width="11.2109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -540,103 +543,143 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="G1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="F2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="F3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H10" s="6" t="s">
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="F4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="F5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="F6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="F7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="F8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="F9" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="F10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H11" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H12" s="6" t="s">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="F11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="F12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H13" s="6" t="s">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="F13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H14" s="6" t="s">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="F14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H15" s="6"/>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H15" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="H1:M7"/>
+    <mergeCell ref="N1:S7"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576" xr:uid="{463C6B66-3722-4578-80F3-D9130B2BE09D}">
